--- a/Tools/Excel/Datas/__tables__.xlsx
+++ b/Tools/Excel/Datas/__tables__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="24052" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -114,6 +114,15 @@
   </si>
   <si>
     <t>Scene</t>
+  </si>
+  <si>
+    <t>game.TbItem</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Item.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1055,14 +1064,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85" outlineLevelRow="4"/>
   <cols>
-    <col min="2" max="2" width="25.875" customWidth="1"/>
-    <col min="3" max="3" width="17.75" customWidth="1"/>
-    <col min="4" max="4" width="50.875" customWidth="1"/>
-    <col min="5" max="5" width="24.375" customWidth="1"/>
-    <col min="6" max="6" width="46.75" customWidth="1"/>
+    <col min="2" max="2" width="25.8761061946903" customWidth="1"/>
+    <col min="3" max="3" width="17.7522123893805" customWidth="1"/>
+    <col min="4" max="4" width="50.8761061946903" customWidth="1"/>
+    <col min="5" max="5" width="24.3716814159292" customWidth="1"/>
+    <col min="6" max="6" width="46.7522123893805" customWidth="1"/>
     <col min="7" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1169,6 +1178,20 @@
       <c r="E4" t="str">
         <f>C4&amp;".xlsx"</f>
         <v>Scene.xlsx</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="2:5">
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
